--- a/results/calibration_results_mean_platt5d.xlsx
+++ b/results/calibration_results_mean_platt5d.xlsx
@@ -1224,16 +1224,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>0.0260600510798394</v>
+        <v>0.0341114686783403</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.0303687149249017</v>
+        <v>0.0326657267417758</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.8366788766788767</v>
+        <v>0.8274969474969475</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.0678570668880064</v>
+        <v>0.06841858290559499</v>
       </c>
     </row>
     <row r="6">
@@ -1272,16 +1272,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>0.0353072762232562</v>
+        <v>0.0328300596575699</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>0.028573757152288</v>
+        <v>0.0203230087741482</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.8375579975579975</v>
+        <v>0.8360439560439561</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.0681968408259913</v>
+        <v>0.06834949014000891</v>
       </c>
     </row>
     <row r="8">
@@ -1504,16 +1504,16 @@
         </is>
       </c>
       <c r="C17" s="1" t="n">
-        <v>0.0197417381592094</v>
+        <v>0.0237031287234276</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.0630647279508412</v>
+        <v>0.0680168697517365</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.7129724208375894</v>
+        <v>0.7060776302349336</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.0920511794890066</v>
+        <v>0.0919566707280798</v>
       </c>
     </row>
     <row r="18">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="C19" s="1" t="n">
-        <v>0.008407225502152</v>
+        <v>0.0085364383743496</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>0.06590136204560661</v>
+        <v>0.0475818804657588</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.5257916241062308</v>
+        <v>0.526046986721144</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.0977322846840494</v>
+        <v>0.0976951118698821</v>
       </c>
     </row>
     <row r="20">
@@ -1830,16 +1830,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>0.0002055465642479</v>
+        <v>0.0002762173963128</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.0110544629067298</v>
+        <v>0.0102832866431563</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.595766129032258</v>
+        <v>0.6617943548387096</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.0079335527989073</v>
+        <v>0.007913245330409199</v>
       </c>
     </row>
     <row r="6">
@@ -1878,16 +1878,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>0.0005746748163085</v>
+        <v>0.0005804956777396</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>0.0131362795449365</v>
+        <v>0.0131390633456571</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.4248991935483871</v>
+        <v>0.4223790322580645</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.0079429239996589</v>
+        <v>0.0079429398750417</v>
       </c>
     </row>
     <row r="8">
@@ -2110,16 +2110,16 @@
         </is>
       </c>
       <c r="C17" s="1" t="n">
-        <v>0.0031846814224627</v>
+        <v>0.003331033450122</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.0107612993748989</v>
+        <v>0.0110316206445349</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.9045226130653268</v>
+        <v>0.9246231155778896</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.0049304604007795</v>
+        <v>0.004926761724516</v>
       </c>
     </row>
     <row r="18">
@@ -2158,16 +2158,16 @@
         </is>
       </c>
       <c r="C19" s="1" t="n">
-        <v>0.00285456811362</v>
+        <v>0.002851811630668</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>0.0110388510243721</v>
+        <v>0.0110376916628278</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>0.7688442211055276</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.0049640651267491</v>
+        <v>0.0049638179474554</v>
       </c>
     </row>
     <row r="20">
@@ -2436,16 +2436,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>0.0797823336652734</v>
+        <v>0.0564491748809814</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.0845849592238664</v>
+        <v>0.1028657380830157</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.6426992314980524</v>
+        <v>0.6522791872828718</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1909877173957252</v>
+        <v>0.1899148505707685</v>
       </c>
     </row>
     <row r="6">
@@ -2484,16 +2484,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>0.0088700498393788</v>
+        <v>0.008683075327286301</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>0.099317354764587</v>
+        <v>0.09944458685460961</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.5085798505105801</v>
+        <v>0.5206863880408463</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.1941779525474872</v>
+        <v>0.1942508168171545</v>
       </c>
     </row>
     <row r="8">
@@ -2716,16 +2716,16 @@
         </is>
       </c>
       <c r="C17" s="1" t="n">
-        <v>0.0663138335105031</v>
+        <v>0.0569414038583636</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.08016392693854869</v>
+        <v>0.0807035791501403</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.5756595636732623</v>
+        <v>0.6068619989852866</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.1942977185809413</v>
+        <v>0.1919447720200565</v>
       </c>
     </row>
     <row r="18">
@@ -2764,16 +2764,16 @@
         </is>
       </c>
       <c r="C19" s="1" t="n">
-        <v>0.0183487157798349</v>
+        <v>0.0716176666802549</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>0.1041933760173994</v>
+        <v>0.0941695692221126</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.6021689497716896</v>
+        <v>0.6253805175038052</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.195548657464131</v>
+        <v>0.1949381057278232</v>
       </c>
     </row>
     <row r="20">
@@ -3042,16 +3042,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>0.044602942764759</v>
+        <v>0.0409236796974873</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.0661013222336769</v>
+        <v>0.0528613575816416</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.6893400716930129</v>
+        <v>0.6910834263775438</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1855853661404867</v>
+        <v>0.1869267030177952</v>
       </c>
     </row>
     <row r="6">
@@ -3090,16 +3090,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>0.0517824057243972</v>
+        <v>0.057882151166305</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>0.0454666756398896</v>
+        <v>0.0537903234560563</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.6906916612798966</v>
+        <v>0.6905545434957199</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.1855416536542819</v>
+        <v>0.1885566072289334</v>
       </c>
     </row>
     <row r="8">
@@ -3322,16 +3322,16 @@
         </is>
       </c>
       <c r="C17" s="1" t="n">
-        <v>0.07554483987390991</v>
+        <v>0.0988146635144948</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.0524315456300973</v>
+        <v>0.101072022691369</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.8428413691571587</v>
+        <v>0.8265243528401423</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.1445291167400114</v>
+        <v>0.150189118132016</v>
       </c>
     </row>
     <row r="18">
@@ -3370,16 +3370,16 @@
         </is>
       </c>
       <c r="C19" s="1" t="n">
-        <v>0.07436075835952501</v>
+        <v>0.0645934361022398</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>0.0658335538741658</v>
+        <v>0.0765615209951442</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.831186357502147</v>
+        <v>0.8293460925039873</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.1482498223664965</v>
+        <v>0.1497677627607748</v>
       </c>
     </row>
     <row r="20">
@@ -3648,16 +3648,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>0.0234770833026795</v>
+        <v>0.0268204004991622</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.0584313000951494</v>
+        <v>0.0465042852220081</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.7046290951075191</v>
+        <v>0.7025364410448838</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1436529792216732</v>
+        <v>0.1446549727715895</v>
       </c>
     </row>
     <row r="6">
@@ -3696,16 +3696,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>0.0371789375207253</v>
+        <v>0.036756165053013</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>0.053045153375367</v>
+        <v>0.0482579440536738</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7030054841968538</v>
+        <v>0.7048816568047337</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.1447752259739189</v>
+        <v>0.1445917528181202</v>
       </c>
     </row>
     <row r="8">
@@ -3928,16 +3928,16 @@
         </is>
       </c>
       <c r="C17" s="1" t="n">
-        <v>0.0388074343894967</v>
+        <v>0.0508745672310342</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.0494656320108045</v>
+        <v>0.0509293888243708</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.7811554151862088</v>
+        <v>0.7826556125806027</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.1797068641076777</v>
+        <v>0.1791193313779527</v>
       </c>
     </row>
     <row r="18">
@@ -3976,16 +3976,16 @@
         </is>
       </c>
       <c r="C19" s="1" t="n">
-        <v>0.0551737354412495</v>
+        <v>0.0478811463523285</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>0.0551157521427839</v>
+        <v>0.0550141025514605</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.7788393209632847</v>
+        <v>0.7778918278720885</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.1826064795796357</v>
+        <v>0.1828052454042991</v>
       </c>
     </row>
     <row r="20">
@@ -4254,16 +4254,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>0.0303326041698455</v>
+        <v>0.0293322855234146</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.0582579566240311</v>
+        <v>0.0560587364435196</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.6422401198042224</v>
+        <v>0.6337478997735408</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.2068452232914008</v>
+        <v>0.2079118232056215</v>
       </c>
     </row>
     <row r="6">
@@ -4302,16 +4302,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>0.043037573225953</v>
+        <v>0.0675958988634682</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>0.085196952952394</v>
+        <v>0.0682452025709889</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.6346245160347725</v>
+        <v>0.6287438819490101</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.2092699348741287</v>
+        <v>0.2107795645358461</v>
       </c>
     </row>
     <row r="8">
@@ -4534,16 +4534,16 @@
         </is>
       </c>
       <c r="C17" s="1" t="n">
-        <v>0.06629721902310839</v>
+        <v>0.0610197532922029</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.0731964475661516</v>
+        <v>0.09650752581655971</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.7445798727213891</v>
+        <v>0.7458742314744904</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.1950470785674399</v>
+        <v>0.1947175172768888</v>
       </c>
     </row>
     <row r="18">
@@ -4582,16 +4582,16 @@
         </is>
       </c>
       <c r="C19" s="1" t="n">
-        <v>0.0741705605072811</v>
+        <v>0.0706533397074416</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>0.0938264417496134</v>
+        <v>0.0637843940173554</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.73929457447956</v>
+        <v>0.7373530363499083</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.1973232706142787</v>
+        <v>0.1971892652814414</v>
       </c>
     </row>
     <row r="20">
@@ -4860,16 +4860,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>0.0477382720708847</v>
+        <v>0.060169622041285</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.0410459154844284</v>
+        <v>0.0587407152280211</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.84245826709062</v>
+        <v>0.8408684419713832</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1593429496603514</v>
+        <v>0.1601246446390918</v>
       </c>
     </row>
     <row r="6">
@@ -4908,16 +4908,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>0.05311773230252</v>
+        <v>0.0503419091019339</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>0.0538658790639865</v>
+        <v>0.0612237164300177</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.8338135930047694</v>
+        <v>0.8337307896131425</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.1624713302642987</v>
+        <v>0.1626005650131539</v>
       </c>
     </row>
     <row r="8">
@@ -5140,16 +5140,16 @@
         </is>
       </c>
       <c r="C17" s="1" t="n">
-        <v>0.0642934729196131</v>
+        <v>0.0629102133288979</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.0672390531934797</v>
+        <v>0.075398990444839</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.7620559704096587</v>
+        <v>0.7282085281596762</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.1800036825960321</v>
+        <v>0.1910759499467099</v>
       </c>
     </row>
     <row r="18">
@@ -5188,16 +5188,16 @@
         </is>
       </c>
       <c r="C19" s="1" t="n">
-        <v>0.0773802743585205</v>
+        <v>0.08681627283809</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>0.0832186683469736</v>
+        <v>0.08616621487158831</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.7193628306232116</v>
+        <v>0.7067834461581408</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.2006647812318973</v>
+        <v>0.2066271560528332</v>
       </c>
     </row>
     <row r="20">
@@ -5466,16 +5466,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>0.0530126131051219</v>
+        <v>0.0620477101691067</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.0655327024930156</v>
+        <v>0.0708762660212815</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.8329767295284536</v>
+        <v>0.8377038032210447</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1643438469670865</v>
+        <v>0.1633380640559222</v>
       </c>
     </row>
     <row r="6">
@@ -5514,16 +5514,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>0.0672173624858665</v>
+        <v>0.0678958133778107</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>0.0735274564543615</v>
+        <v>0.073954757100471</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.8356636977326632</v>
+        <v>0.8355807666152493</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.1638630026167679</v>
+        <v>0.1640010055809327</v>
       </c>
     </row>
     <row r="8">
@@ -5746,16 +5746,16 @@
         </is>
       </c>
       <c r="C17" s="1" t="n">
-        <v>0.0599342763237655</v>
+        <v>0.0581201290525496</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.0476276184730231</v>
+        <v>0.0681364729441702</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.799400074990626</v>
+        <v>0.7987604490615144</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.1439245914963808</v>
+        <v>0.1471212720920504</v>
       </c>
     </row>
     <row r="18">
@@ -5794,16 +5794,16 @@
         </is>
       </c>
       <c r="C19" s="1" t="n">
-        <v>0.0607559235325155</v>
+        <v>0.060693861204388</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>0.0561883278728386</v>
+        <v>0.0518203402546</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.8033701669644235</v>
+        <v>0.8028628774344384</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.1471075545473904</v>
+        <v>0.1476153836576534</v>
       </c>
     </row>
     <row r="20">
